--- a/monitor_xlsx/20260130.xlsx
+++ b/monitor_xlsx/20260130.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2663,6 +2663,112 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>908</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3481</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>-41</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2237</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-419</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1376</v>
+      </c>
+      <c r="J22" t="n">
+        <v>237</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2444</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11777</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-47615</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-11.19</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4328</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>-901</v>
+      </c>
+      <c r="G23" t="n">
+        <v>280</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-442</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1665</v>
+      </c>
+      <c r="J23" t="n">
+        <v>182</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2751</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13202</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-140184</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260130.xlsx
+++ b/monitor_xlsx/20260130.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2769,6 +2769,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>962</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>826</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>308</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-48</v>
+      </c>
+      <c r="L24" t="n">
+        <v>92</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260130.xlsx
+++ b/monitor_xlsx/20260130.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -2822,6 +2822,59 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>180</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2556</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>504</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-840</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J25" t="n">
+        <v>32</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6320</v>
+      </c>
+      <c r="L25" t="n">
+        <v>33424</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-58795</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
